--- a/www/download/IND.hours_worked.empe_ls.r.pc.rpPE.xlsx
+++ b/www/download/IND.hours_worked.empe_ls.r.pc.rpPE.xlsx
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Petrovic</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -673,7 +678,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Austrália</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -683,84 +688,84 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>22.31</t>
+          <t>0.22310560690545</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>21.88</t>
+          <t>0.218792157489448</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>21.08</t>
+          <t>0.210797014493416</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>19.62</t>
+          <t>0.196154708521024</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>18.55</t>
+          <t>0.185471236222602</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>17.34</t>
+          <t>0.173367479976438</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>16.62</t>
+          <t>0.166177842754383</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>16.41</t>
+          <t>0.164082245748724</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>17.51</t>
+          <t>0.175138787685894</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>16.28</t>
+          <t>0.162808496210403</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>0.160027752263217</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>16.42</t>
+          <t>0.164151654007444</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>17.32</t>
+          <t>0.173189113621801</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>17.95</t>
+          <t>0.179517670251248</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>17.81</t>
+          <t>0.178104147881464</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Áustria</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -770,84 +775,84 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>7.33</t>
+          <t>0.0732609242306546</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>6.94</t>
+          <t>0.0694145141090567</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>6.62</t>
+          <t>0.0662468885670925</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>6.43</t>
+          <t>0.0642962556473465</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>6.05</t>
+          <t>0.0605050785876762</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>5.73</t>
+          <t>0.0573047353737073</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>5.47</t>
+          <t>0.0546627869384606</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>5.31</t>
+          <t>0.0530891853335306</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>5.82</t>
+          <t>0.0581888618709785</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>4.79</t>
+          <t>0.0479206398136239</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>4.81</t>
+          <t>0.04812634666422</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>5.25</t>
+          <t>0.0524861511368556</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>5.8</t>
+          <t>0.0580055963237884</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>5.81</t>
+          <t>0.0580623930638642</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>5.17</t>
+          <t>0.0516637321480499</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Bélgica</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -857,84 +862,84 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>16.99</t>
+          <t>0.16993756733088</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>16.13</t>
+          <t>0.161327235258748</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>15.22</t>
+          <t>0.152242107221687</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>13.98</t>
+          <t>0.139778249250483</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>13.2</t>
+          <t>0.131973257865756</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>11.91</t>
+          <t>0.119110796596128</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>11.19</t>
+          <t>0.111913245763758</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>10.83</t>
+          <t>0.108292965063088</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>11.38</t>
+          <t>0.113797443891273</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>9.6</t>
+          <t>0.0960162346469096</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>9.23</t>
+          <t>0.0923009214316938</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>9.05</t>
+          <t>0.0905463901858312</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>8.99</t>
+          <t>0.0899408445271269</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>8.49</t>
+          <t>0.0848542792585045</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>8.14</t>
+          <t>0.0814373873471467</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -944,84 +949,84 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>50.38</t>
+          <t>0.503791663535365</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>49.95</t>
+          <t>0.499450031696226</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>51.91</t>
+          <t>0.519098879722869</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>53.05</t>
+          <t>0.530460199943508</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>50.27</t>
+          <t>0.502726072944004</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>48.42</t>
+          <t>0.48424989472332</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>47.53</t>
+          <t>0.475324255046371</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>47.26</t>
+          <t>0.472573531917062</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>46.13</t>
+          <t>0.461253024525203</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>43.48</t>
+          <t>0.434824414537904</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>42.7</t>
+          <t>0.426987796926467</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>41.77</t>
+          <t>0.417733726805691</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>42.79</t>
+          <t>0.427880180087895</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>42.07</t>
+          <t>0.420694938709067</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>39.09</t>
+          <t>0.39092948835017</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Brasil</t>
+          <t>33</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1031,84 +1036,84 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>29.97</t>
+          <t>0.2996704870769</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>28.97</t>
+          <t>0.2896754327238</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>27.63</t>
+          <t>0.276333127750926</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>25.63</t>
+          <t>0.256256919127745</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>24.12</t>
+          <t>0.241156462132783</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>22.51</t>
+          <t>0.225050077038025</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>21.49</t>
+          <t>0.214897601737295</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>20.75</t>
+          <t>0.207478451629117</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>21.03</t>
+          <t>0.210335581469272</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>19.18</t>
+          <t>0.191762752350571</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>18.43</t>
+          <t>0.184253278769192</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>17.56</t>
+          <t>0.175643894057153</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>17.19</t>
+          <t>0.171853928722805</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>16.56</t>
+          <t>0.16556887885911</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>15.3</t>
+          <t>0.153044275350078</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Canadá</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1118,84 +1123,84 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>0.0206699877592223</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>0.019768047914165</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>0.0182879369295232</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>0.0168006425673112</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>0.0145521395457122</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>0.0130565287391608</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>0.0120892823871877</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>0.0123406836055911</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>0.0130705057865383</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>0.0117607786288215</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>0.011111950141083</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>0.0111643119905234</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>0.0104877314485285</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>0.010815729028485</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>0.0105861343208707</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>35</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1205,84 +1210,84 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>23.73</t>
+          <t>0.237292095099115</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>23.33</t>
+          <t>0.233262779399042</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>22.59</t>
+          <t>0.22589767093495</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>21.3</t>
+          <t>0.212953201884612</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>20.31</t>
+          <t>0.203115189084499</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>19.25</t>
+          <t>0.192455108501965</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>18.6</t>
+          <t>0.185990499701091</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>18.17</t>
+          <t>0.181711865827188</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>19.61</t>
+          <t>0.196087097652196</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>19.28</t>
+          <t>0.192750927899069</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>19.38</t>
+          <t>0.193810240473795</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>19.66</t>
+          <t>0.196645431639415</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>21.04</t>
+          <t>0.210361241147289</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>21.24</t>
+          <t>0.212386014228633</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>21.14</t>
+          <t>0.211413216853391</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Chipre</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1292,84 +1297,84 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>11.77</t>
+          <t>0.117652422176104</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>11.72</t>
+          <t>0.117197380404507</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>12.81</t>
+          <t>0.12806916187873</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>13.6</t>
+          <t>0.135972706223814</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>12.1</t>
+          <t>0.120962216559736</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>11.1</t>
+          <t>0.1109936907617</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>10.77</t>
+          <t>0.107675310904011</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>10.51</t>
+          <t>0.105052714535898</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>10.72</t>
+          <t>0.107199719165062</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>9.96</t>
+          <t>0.0995578928813832</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>10.18</t>
+          <t>0.101834395875418</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>9.88</t>
+          <t>0.0988232468090778</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>9.8</t>
+          <t>0.0980261767650918</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>9.43</t>
+          <t>0.0943325059125545</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>0.0900127744228161</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>República Tcheca</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1379,84 +1384,84 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2.9</t>
+          <t>0.0290029119952918</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2.95</t>
+          <t>0.0294981233152117</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2.93</t>
+          <t>0.0293475331570133</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2.81</t>
+          <t>0.0280569942680268</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2.69</t>
+          <t>0.0269085465156093</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2.48</t>
+          <t>0.0247882069149978</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2.33</t>
+          <t>0.0232570508837974</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>0.0219935732550058</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2.27</t>
+          <t>0.022710676027525</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>0.0196518741947433</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>0.018274152468983</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>0.0187547887395697</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>0.0203932163302459</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>0.0207193613758765</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>0.0187585135807322</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Alemanha</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1466,84 +1471,84 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>0.0490071880296206</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>0.0489634961289295</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>4.82</t>
+          <t>0.0482284085915419</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>4.38</t>
+          <t>0.0437583079375319</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>4.45</t>
+          <t>0.0444666373534184</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>4.46</t>
+          <t>0.0446411373660892</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>4.43</t>
+          <t>0.0442994616721926</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>4.32</t>
+          <t>0.0431824671917275</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>4.53</t>
+          <t>0.0452816821731654</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>4.13</t>
+          <t>0.0413474595527933</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>4.63</t>
+          <t>0.0463177010654461</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>4.78</t>
+          <t>0.0477930141312771</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>4.79</t>
+          <t>0.04789628128692</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>4.73</t>
+          <t>0.0472828193045768</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>4.49</t>
+          <t>0.0449470144528174</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Dinamarca</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1553,84 +1558,84 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>8.78</t>
+          <t>0.0877658308054273</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>8.38</t>
+          <t>0.0838247105886048</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>7.94</t>
+          <t>0.0794373071132994</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>7.2</t>
+          <t>0.0719626174403853</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>6.75</t>
+          <t>0.0674754323497371</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>6.4</t>
+          <t>0.0639726497640605</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>6.09</t>
+          <t>0.0609390526971427</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>5.87</t>
+          <t>0.0587130967216971</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>6.54</t>
+          <t>0.065407498312777</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>6.29</t>
+          <t>0.0629040628817923</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>6.58</t>
+          <t>0.0657738689493405</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>6.69</t>
+          <t>0.066872330229602</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>9.66</t>
+          <t>0.0965675470541575</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>8.93</t>
+          <t>0.0893112774430127</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>9.36</t>
+          <t>0.0936403118202773</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Espanha</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1640,84 +1645,84 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>29.09</t>
+          <t>0.290897075406028</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>26.49</t>
+          <t>0.264907913509078</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>25.28</t>
+          <t>0.252795760782724</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>22.3</t>
+          <t>0.222984317104338</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>20.69</t>
+          <t>0.206920072222181</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>18.26</t>
+          <t>0.1825886850309</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>17.49</t>
+          <t>0.174946874693548</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>16.8</t>
+          <t>0.167954262260771</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>17.31</t>
+          <t>0.173069878642335</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>15.74</t>
+          <t>0.157423487724821</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>14.55</t>
+          <t>0.145454975267328</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>14.26</t>
+          <t>0.142636546385243</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>14.69</t>
+          <t>0.146878155635072</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>15.09</t>
+          <t>0.150875950569604</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>14.26</t>
+          <t>0.142551137387855</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Estônia</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1727,84 +1732,84 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2.71</t>
+          <t>0.027139594358816</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2.69</t>
+          <t>0.0269465178893407</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2.98</t>
+          <t>0.029766533676575</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>3.18</t>
+          <t>0.0318054356635394</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2.77</t>
+          <t>0.0276522768575954</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2.53</t>
+          <t>0.0253171822480964</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2.45</t>
+          <t>0.0245123479854871</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2.39</t>
+          <t>0.0238728094556346</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0.029969752755377</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>2.59</t>
+          <t>0.0259166858644868</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2.38</t>
+          <t>0.0237622188870618</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>2.8</t>
+          <t>0.0280350934593832</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>2.69</t>
+          <t>0.026917337828732</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>2.89</t>
+          <t>0.028910078428593</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>2.53</t>
+          <t>0.0252899622653088</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Finlândia</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1814,84 +1819,84 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>8.56</t>
+          <t>0.0855744870573762</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>0.0814769489932004</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>7.72</t>
+          <t>0.0772120016541068</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>7.29</t>
+          <t>0.0728773516799184</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>6.86</t>
+          <t>0.0685735142747391</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>6.39</t>
+          <t>0.0639373084918213</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>6.13</t>
+          <t>0.0613223719680901</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>5.94</t>
+          <t>0.0594472071218293</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>6.17</t>
+          <t>0.0616701907124454</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>5.38</t>
+          <t>0.0537758254830274</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>5.42</t>
+          <t>0.0541845857447165</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>5.35</t>
+          <t>0.0535437965813387</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>5.52</t>
+          <t>0.0551694191226095</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>5.57</t>
+          <t>0.0557184050169302</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>4.95</t>
+          <t>0.0494876540317666</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>França</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1901,84 +1906,84 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>13.22</t>
+          <t>0.132234470965802</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>12.97</t>
+          <t>0.129684410261872</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>12.21</t>
+          <t>0.122095716339334</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>0.109951153219878</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>10.09</t>
+          <t>0.100905647045158</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>9.33</t>
+          <t>0.0932539177073643</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>8.83</t>
+          <t>0.0882714813800801</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>8.45</t>
+          <t>0.0845412544953061</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>8.9</t>
+          <t>0.0889935450357389</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>8.24</t>
+          <t>0.0823972950615956</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>7.89</t>
+          <t>0.0789285955203655</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>7.9</t>
+          <t>0.0790348620395362</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>7.92</t>
+          <t>0.0792113267460693</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>7.77</t>
+          <t>0.0777288753704419</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>7.44</t>
+          <t>0.0743894018435994</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Reino Unido</t>
+          <t>30</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1988,84 +1993,84 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>12.87</t>
+          <t>0.12867786377491</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>12.67</t>
+          <t>0.126663584082718</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>10.9</t>
+          <t>0.109010311171892</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>9.78</t>
+          <t>0.0977920935045514</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>8.91</t>
+          <t>0.0890725258911645</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>8.21</t>
+          <t>0.0820860072538273</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>8.22</t>
+          <t>0.0821939656740152</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>7.69</t>
+          <t>0.0769105577604131</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>7.61</t>
+          <t>0.0760720502262803</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>6.96</t>
+          <t>0.0696466894548406</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>6.92</t>
+          <t>0.0691714693161082</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>6.82</t>
+          <t>0.0681549060664335</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>7.25</t>
+          <t>0.0724947250627501</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>7.41</t>
+          <t>0.0740664648304557</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>6.92</t>
+          <t>0.0692300634805251</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Grécia</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2075,84 +2080,84 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>20.92</t>
+          <t>0.2091881240701</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>20.27</t>
+          <t>0.202711707159074</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>18.85</t>
+          <t>0.188518137998382</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>16.97</t>
+          <t>0.169651100870229</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>15.84</t>
+          <t>0.158428542563973</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>14.89</t>
+          <t>0.148934032682492</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>15.12</t>
+          <t>0.151237379176534</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>14.13</t>
+          <t>0.141265640331481</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>14.5</t>
+          <t>0.14499102989609</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>12.25</t>
+          <t>0.122486068238353</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>12.35</t>
+          <t>0.123535976040403</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>13.93</t>
+          <t>0.139250597964732</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>14.19</t>
+          <t>0.141875646008444</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>13.94</t>
+          <t>0.139387319517813</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>13.95</t>
+          <t>0.139540856234492</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Hungria</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2162,84 +2167,84 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>6.18</t>
+          <t>0.061753049985124</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>6.27</t>
+          <t>0.0626905873739285</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>6.23</t>
+          <t>0.0623350014973444</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>5.96</t>
+          <t>0.0596174958984162</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>4.66</t>
+          <t>0.0465713737205574</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>5.34</t>
+          <t>0.0533559872850632</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>5.21</t>
+          <t>0.0520794897611961</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>4.99</t>
+          <t>0.0498860349726628</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>5.15</t>
+          <t>0.0515324349691658</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>4.61</t>
+          <t>0.0460502510664775</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>4.58</t>
+          <t>0.0457695224936847</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>4.35</t>
+          <t>0.04347516047987</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>0.045023686230664</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>4.62</t>
+          <t>0.0462340171402905</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>4.09</t>
+          <t>0.0408823630497574</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Indonésia</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2249,84 +2254,84 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>41.61</t>
+          <t>0.416119468881517</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>40.03</t>
+          <t>0.400340896325282</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>39.45</t>
+          <t>0.394517086750007</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>0.360044558651675</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>35.2</t>
+          <t>0.351993890796417</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>30.53</t>
+          <t>0.305271910208268</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>30.94</t>
+          <t>0.309366682971949</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>30.94</t>
+          <t>0.309418605080002</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>30.87</t>
+          <t>0.308741195780695</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>29.89</t>
+          <t>0.298883011670352</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>29.48</t>
+          <t>0.294808991212036</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>29.25</t>
+          <t>0.292506417274527</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>31.03</t>
+          <t>0.310289019103722</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>31.86</t>
+          <t>0.31860671358464</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>31.7</t>
+          <t>0.31701002106702</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Índia</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2336,84 +2341,84 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>23.5</t>
+          <t>0.235003949146351</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>23.02</t>
+          <t>0.230181286536197</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>22.24</t>
+          <t>0.222360369999404</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>20.9</t>
+          <t>0.208970002540333</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>19.91</t>
+          <t>0.199133163684823</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>18.94</t>
+          <t>0.189394409448924</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>18.43</t>
+          <t>0.184305403810359</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>18.15</t>
+          <t>0.181531941147052</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>19.01</t>
+          <t>0.190086048870676</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>17.96</t>
+          <t>0.179572187983495</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>18.25</t>
+          <t>0.182510115116927</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>18.65</t>
+          <t>0.186539000646723</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>19.52</t>
+          <t>0.195156778680385</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>20.12</t>
+          <t>0.201157143810935</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>0.199953142474599</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Irlanda</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2423,84 +2428,84 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>13.71</t>
+          <t>0.13708224629578</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>12.55</t>
+          <t>0.125519563787542</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>11.98</t>
+          <t>0.119773447763192</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>10.97</t>
+          <t>0.109679147784364</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>10.28</t>
+          <t>0.10277602137621</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>9.92</t>
+          <t>0.0991757564100499</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>9.92</t>
+          <t>0.0991756400711481</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>9.4</t>
+          <t>0.094022930610754</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>9.49</t>
+          <t>0.0949406072553918</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>8.64</t>
+          <t>0.0863817356809393</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>8.46</t>
+          <t>0.0845576032234115</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>8.03</t>
+          <t>0.0802540812310105</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>7.96</t>
+          <t>0.0796304540848623</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>7.87</t>
+          <t>0.0786664392999699</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>6.81</t>
+          <t>0.0680621541874028</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Itália</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2510,84 +2515,84 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>29.26</t>
+          <t>0.292639684364485</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>28.05</t>
+          <t>0.280465639415077</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>26.44</t>
+          <t>0.264370945419262</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>24.24</t>
+          <t>0.242380044201909</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>22.5</t>
+          <t>0.224987709442208</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>20.15</t>
+          <t>0.201529534276513</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>21.18</t>
+          <t>0.211820422038209</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>20.61</t>
+          <t>0.206051194895831</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>20.72</t>
+          <t>0.207154178390381</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>18.99</t>
+          <t>0.189923601755041</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>18.14</t>
+          <t>0.18138657963426</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>17.48</t>
+          <t>0.174751804930592</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>17.82</t>
+          <t>0.178186394308897</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>17.39</t>
+          <t>0.173920028105167</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>16.92</t>
+          <t>0.169244098865551</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Japão</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2597,84 +2602,84 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>5.49</t>
+          <t>0.0548838874608763</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>5.14</t>
+          <t>0.0514071487513508</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>0.0475422396594321</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>4.1</t>
+          <t>0.040953476105184</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>3.63</t>
+          <t>0.0363398920476187</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>3.26</t>
+          <t>0.0326407750522996</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>2.89</t>
+          <t>0.0288947488719708</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>2.7</t>
+          <t>0.0270136058646161</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>2.66</t>
+          <t>0.0265825595894368</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>2.51</t>
+          <t>0.0250964306290534</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2.58</t>
+          <t>0.0257540054191387</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>2.65</t>
+          <t>0.0265387117695811</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>2.83</t>
+          <t>0.0282665280050932</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>2.95</t>
+          <t>0.0294989961346314</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>2.92</t>
+          <t>0.0292390796490938</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Coreia do Sul</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2684,84 +2689,84 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>7.34</t>
+          <t>0.0733851252131345</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>6.82</t>
+          <t>0.0682178406036729</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>6.3</t>
+          <t>0.0630318518100447</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>5.17</t>
+          <t>0.051690095234406</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>4.84</t>
+          <t>0.0484163947098176</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>4.43</t>
+          <t>0.0442800406253279</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>3.9</t>
+          <t>0.0390092656989851</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>3.32</t>
+          <t>0.0332034690188854</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>3.42</t>
+          <t>0.0342156542316028</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>2.87</t>
+          <t>0.0287104365732828</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2.61</t>
+          <t>0.0261302245573123</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>2.69</t>
+          <t>0.0269308971125196</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t>0.0287856362477763</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>3.01</t>
+          <t>0.0300979214434053</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>2.97</t>
+          <t>0.0297288780097088</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Lituânia</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2771,84 +2776,84 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>0.0235111012387795</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>0.0234192602632656</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2.58</t>
+          <t>0.0258016189330191</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>0.0274860209000473</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>2.42</t>
+          <t>0.0241652089878893</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>0.0225006877796653</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>0.0219917529059049</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>0.0210490677829655</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>2.13</t>
+          <t>0.0212531800455728</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>0.0210376493736961</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>0.0195190670604044</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>0.0191604171379914</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>0.0219948979539834</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>0.01741275207382</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>0.0159822264622145</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Luxemburgo</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2858,84 +2863,84 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>19.39</t>
+          <t>0.193850552892628</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>20.31</t>
+          <t>0.203076540288751</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>17.72</t>
+          <t>0.177180687170698</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>14.77</t>
+          <t>0.147672347195015</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>12.47</t>
+          <t>0.124721387177165</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>12.38</t>
+          <t>0.123837763113866</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>12.66</t>
+          <t>0.126580564927413</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>12.74</t>
+          <t>0.127415531575685</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>16.93</t>
+          <t>0.169347573163429</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>11.65</t>
+          <t>0.116506503851193</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>10.9</t>
+          <t>0.10895787738473</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>12.99</t>
+          <t>0.129917606334597</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>13.21</t>
+          <t>0.132053362239476</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>13.72</t>
+          <t>0.137183240106629</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>8.68</t>
+          <t>0.0868156365772446</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Letônia</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2945,84 +2950,84 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>4.16</t>
+          <t>0.0415971307140756</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>4.16</t>
+          <t>0.0416156780273808</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>4.56</t>
+          <t>0.045584636114758</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>4.82</t>
+          <t>0.0482385170424977</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>4.22</t>
+          <t>0.0421559149770162</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>3.93</t>
+          <t>0.0392693567756481</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>3.83</t>
+          <t>0.0382747631290128</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>3.69</t>
+          <t>0.036901332087571</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>4.01</t>
+          <t>0.0400513468176645</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>3.39</t>
+          <t>0.0338809704869489</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>3.9</t>
+          <t>0.0389656718024043</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>3.86</t>
+          <t>0.0386387839322717</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>4.32</t>
+          <t>0.0431659703711842</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>4.03</t>
+          <t>0.0403104906591707</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>3.65</t>
+          <t>0.0364646949434878</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>México</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3032,84 +3037,84 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>17.56</t>
+          <t>0.175641524331279</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>17.96</t>
+          <t>0.179578121371147</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>16.61</t>
+          <t>0.166086941151387</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>16.2</t>
+          <t>0.162003203891811</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>16.07</t>
+          <t>0.160703668673144</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>15.46</t>
+          <t>0.154630204340967</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>14.6</t>
+          <t>0.146029632896385</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>14.5</t>
+          <t>0.145028439717364</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>14.99</t>
+          <t>0.149928192969863</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>13.88</t>
+          <t>0.138798236678794</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>13.86</t>
+          <t>0.138623452314122</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>13.75</t>
+          <t>0.137518465286822</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>14.37</t>
+          <t>0.143737052788957</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>14.81</t>
+          <t>0.148105869754173</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>14.72</t>
+          <t>0.147232016479167</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Malta</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3119,84 +3124,84 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>50.38</t>
+          <t>0.503791663535365</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>49.95</t>
+          <t>0.499450031696226</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>51.91</t>
+          <t>0.519098879722869</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>53.05</t>
+          <t>0.530460199943508</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>50.27</t>
+          <t>0.502726072944004</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>48.42</t>
+          <t>0.48424989472332</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>47.53</t>
+          <t>0.475324255046371</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>47.26</t>
+          <t>0.472573531917062</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>46.13</t>
+          <t>0.461253024525203</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>43.48</t>
+          <t>0.434824414537904</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>42.7</t>
+          <t>0.426987796926467</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>41.77</t>
+          <t>0.417733726805691</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>42.79</t>
+          <t>0.427880180087895</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>42.07</t>
+          <t>0.420694938709067</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>39.09</t>
+          <t>0.39092948835017</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Países Baixos</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3206,84 +3211,84 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>14.15</t>
+          <t>0.141475584761822</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>13.19</t>
+          <t>0.131923537352463</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>12.31</t>
+          <t>0.123089598790334</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>11.99</t>
+          <t>0.119899395722205</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>10.47</t>
+          <t>0.104743569073163</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>12.01</t>
+          <t>0.120078407363873</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>12.16</t>
+          <t>0.121619561555749</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>10.58</t>
+          <t>0.105750906385758</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>10.56</t>
+          <t>0.105582035253152</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>9.23</t>
+          <t>0.0922976602923757</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>9.17</t>
+          <t>0.0917077160889435</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>9.5</t>
+          <t>0.0950420438748474</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>9.87</t>
+          <t>0.0986744488711026</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>10.44</t>
+          <t>0.104380709660577</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>10.13</t>
+          <t>0.101342893172297</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Polônia</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3293,84 +3298,84 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>3.18</t>
+          <t>0.0318393144762765</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>3.24</t>
+          <t>0.0323614681815792</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>3.22</t>
+          <t>0.0321925068714985</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>3.08</t>
+          <t>0.0307920710999758</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0.0300321031989641</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2.9</t>
+          <t>0.0290291644597559</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>2.83</t>
+          <t>0.0283463047057471</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>2.57</t>
+          <t>0.0257435116493734</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>2.48</t>
+          <t>0.0247808714447141</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>0.0210333952532026</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0.0199591736735017</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>1.99</t>
+          <t>0.0198583341915391</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>2.16</t>
+          <t>0.0215632340371793</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>0.0229497050798637</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>0.0214919705532899</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3380,84 +3385,84 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>50.38</t>
+          <t>0.503791663535365</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>49.95</t>
+          <t>0.499450031696226</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>51.91</t>
+          <t>0.519098879722869</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>53.05</t>
+          <t>0.530460199943508</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>50.27</t>
+          <t>0.502726072944004</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>48.42</t>
+          <t>0.48424989472332</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>47.53</t>
+          <t>0.475324255046371</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>47.26</t>
+          <t>0.472573531917062</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>46.13</t>
+          <t>0.461253024525203</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>43.48</t>
+          <t>0.434824414537904</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>42.7</t>
+          <t>0.426987796926467</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>41.77</t>
+          <t>0.417733726805691</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>42.79</t>
+          <t>0.427880180087895</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>42.07</t>
+          <t>0.420694938709067</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>39.09</t>
+          <t>0.39092948835017</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Romênia</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3467,84 +3472,84 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>50.38</t>
+          <t>0.503791663535365</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>49.95</t>
+          <t>0.499450031696226</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>51.91</t>
+          <t>0.519098879722869</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>53.05</t>
+          <t>0.530460199943508</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>50.27</t>
+          <t>0.502726072944004</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>48.42</t>
+          <t>0.48424989472332</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>47.53</t>
+          <t>0.475324255046371</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>47.26</t>
+          <t>0.472573531917062</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>46.13</t>
+          <t>0.461253024525203</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>43.48</t>
+          <t>0.434824414537904</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>42.7</t>
+          <t>0.426987796926467</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>41.77</t>
+          <t>0.417733726805691</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>42.79</t>
+          <t>0.427880180087895</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>42.07</t>
+          <t>0.420694938709067</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>39.09</t>
+          <t>0.39092948835017</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Rússia</t>
+          <t>43</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3554,84 +3559,84 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>3.11</t>
+          <t>0.0310641356269143</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>3.16</t>
+          <t>0.0315962764463119</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>3.14</t>
+          <t>0.0314383840941004</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>3.01</t>
+          <t>0.0300663815735025</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>2.89</t>
+          <t>0.0288948467690914</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2.67</t>
+          <t>0.026654840398538</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>0.0250273298803271</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>0.0236798327228689</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>2.39</t>
+          <t>0.0238507420933425</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>0.0206982325618201</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0.0199812643612804</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>2.06</t>
+          <t>0.0205959465254105</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>2.19</t>
+          <t>0.0219007033156253</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>0.0228389494021241</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>2.27</t>
+          <t>0.0226914814021017</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Eslováquia</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3641,84 +3646,84 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>2.8</t>
+          <t>0.0279726774786522</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2.84</t>
+          <t>0.028443472930857</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2.83</t>
+          <t>0.0282934665146294</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2.7</t>
+          <t>0.0270404465120127</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>0.0214971482323575</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>0.0185020646927274</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>0.017115016358873</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>0.0152992404613841</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>0.0160574276959458</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>0.0146889027090854</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>0.0137756146938047</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>0.0138548263437881</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>0.0144013083629224</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>0.0152106047847529</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>0.0133178262331937</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Eslovênia</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3728,84 +3733,84 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>6.32</t>
+          <t>0.0631558321567276</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>6.41</t>
+          <t>0.0640868155436045</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>6.37</t>
+          <t>0.0637442611483384</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>6.11</t>
+          <t>0.0610827521438488</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>5.35</t>
+          <t>0.0535420224105819</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>5.11</t>
+          <t>0.0511004225084662</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>5.8</t>
+          <t>0.0580499641350243</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>5.25</t>
+          <t>0.052464944074821</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>5.31</t>
+          <t>0.0530646540662677</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>4.65</t>
+          <t>0.0465372404605451</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>0.0450332816074003</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>4.31</t>
+          <t>0.0431253349622306</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>4.58</t>
+          <t>0.0457524199961825</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>4.64</t>
+          <t>0.0463813521013895</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>4.26</t>
+          <t>0.0425875099197261</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Suécia</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3815,84 +3820,84 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>9.95</t>
+          <t>0.0995434537180569</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>9.75</t>
+          <t>0.0974650771646323</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>9.22</t>
+          <t>0.0922342219241927</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>8.46</t>
+          <t>0.0845781911555234</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>8.11</t>
+          <t>0.0811469541255874</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>6.63</t>
+          <t>0.0663052596228705</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>6.24</t>
+          <t>0.0623708553635282</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>6.08</t>
+          <t>0.0607839610717715</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>6.34</t>
+          <t>0.0634443803261673</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>5.84</t>
+          <t>0.0583636756473658</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>5.58</t>
+          <t>0.0557638277281777</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>5.49</t>
+          <t>0.0548909549459192</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>5.64</t>
+          <t>0.0564122025631577</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>5.48</t>
+          <t>0.0547739762614651</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>6.06</t>
+          <t>0.0605953689592853</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Turquia</t>
+          <t>42</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3902,84 +3907,84 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>40.4</t>
+          <t>0.404045130081286</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>38.67</t>
+          <t>0.386702071432917</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>36.95</t>
+          <t>0.369502588493074</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>35.75</t>
+          <t>0.357535516676864</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>33.73</t>
+          <t>0.337314745915502</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>31.8</t>
+          <t>0.318040491134297</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>30.16</t>
+          <t>0.301600006655166</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>28.99</t>
+          <t>0.289939417135663</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>28.9</t>
+          <t>0.288955630733143</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>29.44</t>
+          <t>0.294422169488935</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>28.51</t>
+          <t>0.285077796245802</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>28.15</t>
+          <t>0.281513501123598</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>28.08</t>
+          <t>0.280845075436418</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>28.05</t>
+          <t>0.280478945944188</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>27.02</t>
+          <t>0.270222874453615</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>China: Taiwan</t>
+          <t>36</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3989,84 +3994,84 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>18.92</t>
+          <t>0.189247082667688</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>18.29</t>
+          <t>0.182943545907765</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>17.42</t>
+          <t>0.174236253778018</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>16.05</t>
+          <t>0.160516752313751</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>15.08</t>
+          <t>0.150820872108581</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>14.03</t>
+          <t>0.140296974825544</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>13.43</t>
+          <t>0.134294849724613</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>13.02</t>
+          <t>0.130156311476819</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>13.62</t>
+          <t>0.136246011060404</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>12.68</t>
+          <t>0.126795900043629</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>12.57</t>
+          <t>0.125734000081705</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>12.2</t>
+          <t>0.122043444406452</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>12.5</t>
+          <t>0.125033877122902</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>12.2</t>
+          <t>0.121974419387373</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>10.36</t>
+          <t>0.103601808582555</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>31</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4076,84 +4081,84 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>4.1</t>
+          <t>0.0410324546331388</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>3.99</t>
+          <t>0.0399294150692271</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>4.15</t>
+          <t>0.0415412362083621</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>3.68</t>
+          <t>0.0367993739730452</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>3.69</t>
+          <t>0.0369318413580229</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>3.4</t>
+          <t>0.0340292712434191</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>3.34</t>
+          <t>0.0334128259415354</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>3.49</t>
+          <t>0.0348908295042781</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>3.98</t>
+          <t>0.0397882071565803</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>3.48</t>
+          <t>0.0348296513428237</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>3.46</t>
+          <t>0.0346490915449813</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>3.59</t>
+          <t>0.0359098814237197</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>3.58</t>
+          <t>0.0358053532513146</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>3.64</t>
+          <t>0.0364111814218859</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>3.35</t>
+          <t>0.0335233174568915</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Resto do mundo</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4163,84 +4168,84 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>13.59</t>
+          <t>0.135859210038903</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>13.34</t>
+          <t>0.13335620553827</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>12.97</t>
+          <t>0.12965355424116</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>12.19</t>
+          <t>0.121926593455995</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>11.41</t>
+          <t>0.114073924596391</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>10.74</t>
+          <t>0.107406794737631</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>10.49</t>
+          <t>0.104900699449064</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>10.2</t>
+          <t>0.102022939339675</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>10.73</t>
+          <t>0.107289121961806</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>9.75</t>
+          <t>0.0975296899642317</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>9.66</t>
+          <t>0.0965877627571182</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>9.72</t>
+          <t>0.0972406352319377</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>10.21</t>
+          <t>0.102132697781099</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>10.28</t>
+          <t>0.102837118175769</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>9.71</t>
+          <t>0.0971311803028804</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Mundo</t>
+          <t>46</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4250,84 +4255,84 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>17.24</t>
+          <t>0.172364533837723</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>16.82</t>
+          <t>0.168225256934705</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>16.5</t>
+          <t>0.165004683792315</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>15.81</t>
+          <t>0.158094274116028</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>14.83</t>
+          <t>0.148292822444621</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>13.99</t>
+          <t>0.139882615601068</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>13.68</t>
+          <t>0.136828033106213</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>13.35</t>
+          <t>0.133475052550757</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>13.61</t>
+          <t>0.136094840323882</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>12.56</t>
+          <t>0.125596642989077</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>12.34</t>
+          <t>0.123416396477692</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>12.3</t>
+          <t>0.123043370044198</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>12.73</t>
+          <t>0.127307319725266</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>12.69</t>
+          <t>0.126871911015322</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>11.96</t>
+          <t>0.119632562917633</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Croácia</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4339,7 +4344,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Suíça</t>
+          <t>44</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4351,7 +4356,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Noruega</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4363,7 +4368,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Africa do Sul</t>
+          <t>45</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4375,7 +4380,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Resto do mundo - Asia</t>
+          <t>47</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4387,7 +4392,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Resto do mundo - America</t>
+          <t>50</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4399,7 +4404,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Resto do mundo - Europa</t>
+          <t>48</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4411,7 +4416,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Resto do mundo - Africa</t>
+          <t>49</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4423,7 +4428,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Resto do mundo - Oriente Medio</t>
+          <t>51</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4470,6 +4475,11 @@
           <t>hours_worked.empe_ls.r.pc</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4504,6 +4514,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Petrovic</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>rpPE</t>
